--- a/Prices/settings_app/price change log.xlsx
+++ b/Prices/settings_app/price change log.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB929E5-FDDD-4FFD-AB7C-42A3D0CDEC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{1DB929E5-FDDD-4FFD-AB7C-42A3D0CDEC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E35E89A-482D-4E80-860A-E8873A6C55F7}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1290" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global_markup" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="66">
   <si>
     <t>BIODERMA Lab</t>
   </si>
@@ -202,9 +202,6 @@
     <t>Разговор с Владимиром</t>
   </si>
   <si>
-    <t>Владимир Орестов, на основании парсера</t>
-  </si>
-  <si>
     <t>28690</t>
   </si>
   <si>
@@ -227,6 +224,12 @@
   </si>
   <si>
     <t>price</t>
+  </si>
+  <si>
+    <t>Запуск новой версии exchange</t>
+  </si>
+  <si>
+    <t>Тестовая запись</t>
   </si>
 </sst>
 </file>
@@ -776,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AL215"/>
+  <dimension ref="A1:AL214"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.7109375" customWidth="1"/>
@@ -857,109 +860,109 @@
       <c r="A2" s="9"/>
       <c r="B2" s="8"/>
       <c r="C2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="O2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="R2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="U2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="X2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y2" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="Z2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="AA2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB2" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="AC2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="AD2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AE2" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="AF2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="AG2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AH2" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="AI2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="AJ2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AK2" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="AL2" s="14" t="s">
         <v>24</v>
@@ -11563,7 +11566,7 @@
     </row>
     <row r="96" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B96" s="15">
         <v>45947.519444444442</v>
@@ -11911,7 +11914,7 @@
     </row>
     <row r="99" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B99" s="15">
         <v>45951.643055555556</v>
@@ -14463,118 +14466,118 @@
     </row>
     <row r="121" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B121" s="15">
-        <v>45982.604861111111</v>
+        <v>46036.615972222222</v>
       </c>
       <c r="C121" s="17">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="D121" s="16">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="E121" s="18">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F121" s="17">
-        <v>2.2000000000000002</v>
+        <v>2.25</v>
       </c>
       <c r="G121" s="16">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="H121" s="18">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="I121" s="17">
-        <v>2.2000000000000002</v>
+        <v>2.25</v>
       </c>
       <c r="J121" s="16">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="K121" s="18">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="L121" s="17">
-        <v>2.2000000000000002</v>
+        <v>2.25</v>
       </c>
       <c r="M121" s="16">
-        <v>2.31</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="N121" s="18">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="O121" s="17">
-        <v>2.2000000000000002</v>
+        <v>2.25</v>
       </c>
       <c r="P121" s="16">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="Q121" s="18">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R121" s="17">
-        <v>2.2000000000000002</v>
+        <v>2.25</v>
       </c>
       <c r="S121" s="16">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="T121" s="18">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U121" s="17">
-        <v>2.2000000000000002</v>
+        <v>2.25</v>
       </c>
       <c r="V121" s="16">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="W121" s="18">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="X121" s="17">
-        <v>2.2000000000000002</v>
+        <v>2.25</v>
       </c>
       <c r="Y121" s="16">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="Z121" s="18">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AA121" s="17">
-        <v>2.2000000000000002</v>
+        <v>2.25</v>
       </c>
       <c r="AB121" s="16">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AC121" s="18">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD121" s="17">
-        <v>2.2000000000000002</v>
+        <v>2.25</v>
       </c>
       <c r="AE121" s="16">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AF121" s="18">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AG121" s="17">
-        <v>2.2000000000000002</v>
+        <v>2.25</v>
       </c>
       <c r="AH121" s="16">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AI121" s="18">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AJ121" s="17">
-        <v>2.2000000000000002</v>
+        <v>2.25</v>
       </c>
       <c r="AK121" s="16">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AL121" s="18">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="122" spans="1:38" x14ac:dyDescent="0.25">
@@ -16294,7 +16297,6 @@
       <c r="AL165" s="18"/>
     </row>
     <row r="166" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B166" s="6"/>
       <c r="C166" s="17"/>
       <c r="D166" s="16"/>
       <c r="E166" s="18"/>
@@ -18156,46 +18158,13 @@
       <c r="AK214" s="16"/>
       <c r="AL214" s="18"/>
     </row>
-    <row r="215" spans="3:38" x14ac:dyDescent="0.25">
-      <c r="C215" s="17"/>
-      <c r="D215" s="16"/>
-      <c r="E215" s="18"/>
-      <c r="F215" s="17"/>
-      <c r="G215" s="16"/>
-      <c r="H215" s="18"/>
-      <c r="I215" s="17"/>
-      <c r="J215" s="16"/>
-      <c r="K215" s="18"/>
-      <c r="L215" s="17"/>
-      <c r="M215" s="16"/>
-      <c r="N215" s="18"/>
-      <c r="O215" s="17"/>
-      <c r="P215" s="16"/>
-      <c r="Q215" s="18"/>
-      <c r="R215" s="17"/>
-      <c r="S215" s="16"/>
-      <c r="T215" s="18"/>
-      <c r="U215" s="17"/>
-      <c r="V215" s="16"/>
-      <c r="W215" s="18"/>
-      <c r="X215" s="17"/>
-      <c r="Y215" s="16"/>
-      <c r="Z215" s="18"/>
-      <c r="AA215" s="17"/>
-      <c r="AB215" s="16"/>
-      <c r="AC215" s="18"/>
-      <c r="AD215" s="17"/>
-      <c r="AE215" s="16"/>
-      <c r="AF215" s="18"/>
-      <c r="AG215" s="17"/>
-      <c r="AH215" s="16"/>
-      <c r="AI215" s="18"/>
-      <c r="AJ215" s="17"/>
-      <c r="AK215" s="16"/>
-      <c r="AL215" s="18"/>
-    </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="AJ1:AL1"/>
     <mergeCell ref="R1:T1"/>
@@ -18203,11 +18172,6 @@
     <mergeCell ref="X1:Z1"/>
     <mergeCell ref="AA1:AC1"/>
     <mergeCell ref="AD1:AF1"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -18252,7 +18216,7 @@
         <v>45975.544444444444</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>41</v>
@@ -18260,31 +18224,39 @@
       <c r="D2" s="11">
         <v>2.65</v>
       </c>
-      <c r="E2" s="13"/>
-      <c r="F2" s="10"/>
+      <c r="E2" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D3" s="11">
         <v>2.65</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="10"/>
+      <c r="E3" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>49</v>
@@ -18292,31 +18264,39 @@
       <c r="D4" s="11">
         <v>2.65</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="10"/>
+      <c r="E4" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D5" s="11">
         <v>2.65</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="10"/>
+      <c r="E5" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>45</v>
@@ -18324,15 +18304,19 @@
       <c r="D6" s="11">
         <v>2.65</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="10"/>
+      <c r="E6" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>31</v>
@@ -18340,15 +18324,19 @@
       <c r="D7" s="11">
         <v>2.65</v>
       </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="10"/>
+      <c r="E7" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>33</v>
@@ -18356,31 +18344,39 @@
       <c r="D8" s="11">
         <v>2.65</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="10"/>
+      <c r="E8" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D9" s="11">
         <v>2.65</v>
       </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="10"/>
+      <c r="E9" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>36</v>
@@ -18388,15 +18384,19 @@
       <c r="D10" s="11">
         <v>2.65</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="10"/>
+      <c r="E10" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>37</v>
@@ -18404,15 +18404,19 @@
       <c r="D11" s="11">
         <v>2.65</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="10"/>
+      <c r="E11" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>39</v>
@@ -18420,15 +18424,19 @@
       <c r="D12" s="11">
         <v>2.65</v>
       </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="10"/>
+      <c r="E12" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>34</v>
@@ -18436,15 +18444,19 @@
       <c r="D13" s="11">
         <v>2.65</v>
       </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="10"/>
+      <c r="E13" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>35</v>
@@ -18452,15 +18464,19 @@
       <c r="D14" s="11">
         <v>2.65</v>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="10"/>
+      <c r="E14" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>43</v>
@@ -18468,15 +18484,19 @@
       <c r="D15" s="11">
         <v>2.65</v>
       </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="10"/>
+      <c r="E15" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>32</v>
@@ -18484,15 +18504,19 @@
       <c r="D16" s="11">
         <v>2.65</v>
       </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="10"/>
+      <c r="E16" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>40</v>
@@ -18500,15 +18524,19 @@
       <c r="D17" s="11">
         <v>2.65</v>
       </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="10"/>
+      <c r="E17" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>48</v>
@@ -18516,15 +18544,19 @@
       <c r="D18" s="11">
         <v>2.65</v>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="10"/>
+      <c r="E18" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>44</v>
@@ -18532,15 +18564,19 @@
       <c r="D19" s="11">
         <v>2.65</v>
       </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="10"/>
+      <c r="E19" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>42</v>
@@ -18548,15 +18584,19 @@
       <c r="D20" s="11">
         <v>2.65</v>
       </c>
-      <c r="E20" s="13"/>
-      <c r="F20" s="10"/>
+      <c r="E20" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>47</v>
@@ -18564,31 +18604,39 @@
       <c r="D21" s="11">
         <v>2.65</v>
       </c>
-      <c r="E21" s="13"/>
-      <c r="F21" s="10"/>
+      <c r="E21" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B22" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="D22" s="11">
         <v>2.65</v>
       </c>
-      <c r="E22" s="13"/>
-      <c r="F22" s="10"/>
+      <c r="E22" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>46</v>
@@ -18596,15 +18644,19 @@
       <c r="D23" s="11">
         <v>2.65</v>
       </c>
-      <c r="E23" s="13"/>
-      <c r="F23" s="10"/>
+      <c r="E23" s="13">
+        <v>45986.582638888889</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13">
         <v>45975.544444444444</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>38</v>
@@ -18615,7 +18667,9 @@
       <c r="E24" s="13">
         <v>45986.582638888889</v>
       </c>
-      <c r="F24" s="10"/>
+      <c r="F24" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>

--- a/Prices/settings_app/price change log.xlsx
+++ b/Prices/settings_app/price change log.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{1DB929E5-FDDD-4FFD-AB7C-42A3D0CDEC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E35E89A-482D-4E80-860A-E8873A6C55F7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01F025F-D7B6-4506-9902-0FF1AEB44573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24645" yWindow="240" windowWidth="23505" windowHeight="13155" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global_markup" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="66">
   <si>
     <t>BIODERMA Lab</t>
   </si>
@@ -779,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AL214"/>
+  <dimension ref="A1:AL212"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.7109375" customWidth="1"/>
@@ -16219,7 +16219,6 @@
       <c r="AL163" s="18"/>
     </row>
     <row r="164" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B164" s="6"/>
       <c r="C164" s="17"/>
       <c r="D164" s="16"/>
       <c r="E164" s="18"/>
@@ -16258,7 +16257,6 @@
       <c r="AL164" s="18"/>
     </row>
     <row r="165" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B165" s="6"/>
       <c r="C165" s="17"/>
       <c r="D165" s="16"/>
       <c r="E165" s="18"/>
@@ -18082,89 +18080,8 @@
       <c r="AK212" s="16"/>
       <c r="AL212" s="18"/>
     </row>
-    <row r="213" spans="3:38" x14ac:dyDescent="0.25">
-      <c r="C213" s="17"/>
-      <c r="D213" s="16"/>
-      <c r="E213" s="18"/>
-      <c r="F213" s="17"/>
-      <c r="G213" s="16"/>
-      <c r="H213" s="18"/>
-      <c r="I213" s="17"/>
-      <c r="J213" s="16"/>
-      <c r="K213" s="18"/>
-      <c r="L213" s="17"/>
-      <c r="M213" s="16"/>
-      <c r="N213" s="18"/>
-      <c r="O213" s="17"/>
-      <c r="P213" s="16"/>
-      <c r="Q213" s="18"/>
-      <c r="R213" s="17"/>
-      <c r="S213" s="16"/>
-      <c r="T213" s="18"/>
-      <c r="U213" s="17"/>
-      <c r="V213" s="16"/>
-      <c r="W213" s="18"/>
-      <c r="X213" s="17"/>
-      <c r="Y213" s="16"/>
-      <c r="Z213" s="18"/>
-      <c r="AA213" s="17"/>
-      <c r="AB213" s="16"/>
-      <c r="AC213" s="18"/>
-      <c r="AD213" s="17"/>
-      <c r="AE213" s="16"/>
-      <c r="AF213" s="18"/>
-      <c r="AG213" s="17"/>
-      <c r="AH213" s="16"/>
-      <c r="AI213" s="18"/>
-      <c r="AJ213" s="17"/>
-      <c r="AK213" s="16"/>
-      <c r="AL213" s="18"/>
-    </row>
-    <row r="214" spans="3:38" x14ac:dyDescent="0.25">
-      <c r="C214" s="17"/>
-      <c r="D214" s="16"/>
-      <c r="E214" s="18"/>
-      <c r="F214" s="17"/>
-      <c r="G214" s="16"/>
-      <c r="H214" s="18"/>
-      <c r="I214" s="17"/>
-      <c r="J214" s="16"/>
-      <c r="K214" s="18"/>
-      <c r="L214" s="17"/>
-      <c r="M214" s="16"/>
-      <c r="N214" s="18"/>
-      <c r="O214" s="17"/>
-      <c r="P214" s="16"/>
-      <c r="Q214" s="18"/>
-      <c r="R214" s="17"/>
-      <c r="S214" s="16"/>
-      <c r="T214" s="18"/>
-      <c r="U214" s="17"/>
-      <c r="V214" s="16"/>
-      <c r="W214" s="18"/>
-      <c r="X214" s="17"/>
-      <c r="Y214" s="16"/>
-      <c r="Z214" s="18"/>
-      <c r="AA214" s="17"/>
-      <c r="AB214" s="16"/>
-      <c r="AC214" s="18"/>
-      <c r="AD214" s="17"/>
-      <c r="AE214" s="16"/>
-      <c r="AF214" s="18"/>
-      <c r="AG214" s="17"/>
-      <c r="AH214" s="16"/>
-      <c r="AI214" s="18"/>
-      <c r="AJ214" s="17"/>
-      <c r="AK214" s="16"/>
-      <c r="AL214" s="18"/>
-    </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="AG1:AI1"/>
     <mergeCell ref="AJ1:AL1"/>
     <mergeCell ref="R1:T1"/>
@@ -18172,6 +18089,11 @@
     <mergeCell ref="X1:Z1"/>
     <mergeCell ref="AA1:AC1"/>
     <mergeCell ref="AD1:AF1"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -18180,7 +18102,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F499"/>
+  <dimension ref="A1:F498"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
@@ -18672,12 +18594,22 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="11"/>
+      <c r="A25" s="13">
+        <v>45975.544444444444</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="11">
+        <v>2.65</v>
+      </c>
       <c r="E25" s="13"/>
-      <c r="F25" s="10"/>
+      <c r="F25" s="10" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
@@ -18786,8 +18718,8 @@
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="13"/>
       <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="11"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
       <c r="E39" s="13"/>
       <c r="F39" s="10"/>
     </row>
@@ -18986,8 +18918,8 @@
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="13"/>
       <c r="B64" s="10"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="11"/>
       <c r="E64" s="13"/>
       <c r="F64" s="10"/>
     </row>
@@ -22463,14 +22395,6 @@
       <c r="E498" s="13"/>
       <c r="F498" s="10"/>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A499" s="13"/>
-      <c r="B499" s="10"/>
-      <c r="C499" s="10"/>
-      <c r="D499" s="11"/>
-      <c r="E499" s="13"/>
-      <c r="F499" s="10"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
